--- a/ig/DM-JUILLET-2026/ValueSet-jdv-modele-document-cda-cisis.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-jdv-modele-document-cda-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="152">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150250</t>
+    <t>20260716085852</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:50+01:00</t>
+    <t>2026-07-16T08:58:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,6 +422,36 @@
   </si>
   <si>
     <t>Fiche de retour du service des urgences</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.11.1.19.1</t>
+  </si>
+  <si>
+    <t>PSIG – Formulaire MSO Rougeole</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.11.1.19.2</t>
+  </si>
+  <si>
+    <t>PSIG – Formulaire MSO Dengue</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.11.1.19.3</t>
+  </si>
+  <si>
+    <t>PSIG – Formulaire MSO Chikungunya</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.11.1.19.4</t>
+  </si>
+  <si>
+    <t>PSIG – Formulaire MSO Zika</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.11.1.19.5</t>
+  </si>
+  <si>
+    <t>PSIG – Formulaire MSO West Nile</t>
   </si>
   <si>
     <t/>
@@ -703,7 +733,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B58"/>
+  <dimension ref="A1:B63"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -1163,15 +1193,55 @@
         <v>136</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B62" t="s" s="2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="B63" t="s" s="2">
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -1198,26 +1268,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>140</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>141</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
